--- a/info/defences/defencesDatabase.xlsx
+++ b/info/defences/defencesDatabase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayuu/Developer/arxstudios/clashex/info/defences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{992362BB-18B5-1B45-BADB-474F5A4CB767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05282831-63B6-FF48-967E-0FD70A9C9E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26160" yWindow="5760" windowWidth="27640" windowHeight="16680" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="34200" windowHeight="21000" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="cannon" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,12 +34,125 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Hitpoints</t>
+  </si>
+  <si>
+    <t>Build Cost</t>
+  </si>
+  <si>
+    <t>5s</t>
+  </si>
+  <si>
+    <t>30s</t>
+  </si>
+  <si>
+    <t>2m</t>
+  </si>
+  <si>
+    <t>20m</t>
+  </si>
+  <si>
+    <t>30m</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>3h 30m</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>4h 30m</t>
+  </si>
+  <si>
+    <t>5h</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>8h</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>11h</t>
+  </si>
+  <si>
+    <t>12h</t>
+  </si>
+  <si>
+    <t>16h</t>
+  </si>
+  <si>
+    <t>20h</t>
+  </si>
+  <si>
+    <t>1d</t>
+  </si>
+  <si>
+    <t>1d 12h</t>
+  </si>
+  <si>
+    <t>DPSec</t>
+  </si>
+  <si>
+    <t>DPShot</t>
+  </si>
+  <si>
+    <t>Build time</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH Required </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -62,13 +175,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -381,9 +501,596 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDC0AC2-6795-D34F-B3EF-6458DFDE8454}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>300</v>
+      </c>
+      <c r="E3" s="2">
+        <v>250</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>360</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>420</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>500</v>
+      </c>
+      <c r="E6" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D7" s="2">
+        <v>600</v>
+      </c>
+      <c r="E7" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2">
+        <v>660</v>
+      </c>
+      <c r="E8" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2">
+        <v>730</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2">
+        <v>84</v>
+      </c>
+      <c r="H9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2">
+        <v>38.4</v>
+      </c>
+      <c r="D10" s="2">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>160000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>103</v>
+      </c>
+      <c r="H10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="D11" s="2">
+        <v>880</v>
+      </c>
+      <c r="E11" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2">
+        <v>112</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2">
+        <v>51.2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>960</v>
+      </c>
+      <c r="E12" s="3">
+        <v>330000</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2">
+        <v>120</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>74</v>
+      </c>
+      <c r="C13" s="2">
+        <v>59.2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1060</v>
+      </c>
+      <c r="E13" s="3">
+        <v>500000</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2">
+        <v>127</v>
+      </c>
+      <c r="H13" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>85</v>
+      </c>
+      <c r="C14" s="2">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1160</v>
+      </c>
+      <c r="E14" s="3">
+        <v>600000</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2">
+        <v>134</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>95</v>
+      </c>
+      <c r="C15" s="2">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1260</v>
+      </c>
+      <c r="E15" s="3">
+        <v>660000</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <v>146</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>100</v>
+      </c>
+      <c r="C16" s="2">
+        <v>80</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1380</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2">
+        <v>169</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>105</v>
+      </c>
+      <c r="C17" s="2">
+        <v>84</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="2">
+        <v>189</v>
+      </c>
+      <c r="H17" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>110</v>
+      </c>
+      <c r="C18" s="2">
+        <v>88</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1620</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2">
+        <v>198</v>
+      </c>
+      <c r="H18" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>115</v>
+      </c>
+      <c r="C19" s="2">
+        <v>92</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1740</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="2">
+        <v>207</v>
+      </c>
+      <c r="H19" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2">
+        <v>100</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1870</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="2">
+        <v>240</v>
+      </c>
+      <c r="H20" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>135</v>
+      </c>
+      <c r="C21" s="2">
+        <v>108</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="2">
+        <v>268</v>
+      </c>
+      <c r="H21" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>150</v>
+      </c>
+      <c r="C22" s="2">
+        <v>120</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2150</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2">
+        <v>293</v>
+      </c>
+      <c r="H22" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>160</v>
+      </c>
+      <c r="C23" s="2">
+        <v>128</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2250</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="2">
+        <v>360</v>
+      </c>
+      <c r="H23" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{81AC77CC-8D9F-3444-A070-BFE353463024}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{7511E465-37B2-DE4A-BD60-F300EA3E2999}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/info/defences/defencesDatabase.xlsx
+++ b/info/defences/defencesDatabase.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayuu/Developer/arxstudios/clashex/info/defences/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\arxstudios\clashex\info\defences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05282831-63B6-FF48-967E-0FD70A9C9E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AA3C6D-8EC6-454A-B32B-E2E65A561D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1000" windowWidth="34200" windowHeight="21000" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="19296" tabRatio="779" firstSheet="1" activeTab="9" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
   </bookViews>
   <sheets>
     <sheet name="cannon" sheetId="1" r:id="rId1"/>
+    <sheet name="archer tower" sheetId="2" r:id="rId2"/>
+    <sheet name="mortar" sheetId="3" r:id="rId3"/>
+    <sheet name="air defense" sheetId="4" r:id="rId4"/>
+    <sheet name="wizard tower" sheetId="5" r:id="rId5"/>
+    <sheet name="air sweeper" sheetId="6" r:id="rId6"/>
+    <sheet name="hidden tesla" sheetId="7" r:id="rId7"/>
+    <sheet name="bomb tower" sheetId="8" r:id="rId8"/>
+    <sheet name="xbow" sheetId="9" r:id="rId9"/>
+    <sheet name="Inferno_Tower" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="71">
   <si>
     <t>Level</t>
   </si>
@@ -122,6 +131,132 @@
   </si>
   <si>
     <t xml:space="preserve">TH Required </t>
+  </si>
+  <si>
+    <t>Damage per Second</t>
+  </si>
+  <si>
+    <t>Damage per Shot</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Build Time</t>
+  </si>
+  <si>
+    <t>Experience Gained</t>
+  </si>
+  <si>
+    <t>Town Hall Level Required</t>
+  </si>
+  <si>
+    <t>15s</t>
+  </si>
+  <si>
+    <t>1h 30m</t>
+  </si>
+  <si>
+    <t>7h</t>
+  </si>
+  <si>
+    <t>1d 6h</t>
+  </si>
+  <si>
+    <t>2d</t>
+  </si>
+  <si>
+    <t>Damage per Hit</t>
+  </si>
+  <si>
+    <t>18h</t>
+  </si>
+  <si>
+    <t>2d 12h</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>4d</t>
+  </si>
+  <si>
+    <t>5d</t>
+  </si>
+  <si>
+    <t>12d 12h</t>
+  </si>
+  <si>
+    <t>4d 12h</t>
+  </si>
+  <si>
+    <t>6d</t>
+  </si>
+  <si>
+    <t>6d 12h</t>
+  </si>
+  <si>
+    <t>7d</t>
+  </si>
+  <si>
+    <t>13d 6h</t>
+  </si>
+  <si>
+    <t>1d 18h</t>
+  </si>
+  <si>
+    <t>5d 12h</t>
+  </si>
+  <si>
+    <t>Push Strength</t>
+  </si>
+  <si>
+    <t>1.6 tiles</t>
+  </si>
+  <si>
+    <t>2.0 tiles</t>
+  </si>
+  <si>
+    <t>2.4 tiles</t>
+  </si>
+  <si>
+    <t>2.8 tiles</t>
+  </si>
+  <si>
+    <t>3.2 tiles</t>
+  </si>
+  <si>
+    <t>3.6 tiles</t>
+  </si>
+  <si>
+    <t>4.0 tiles</t>
+  </si>
+  <si>
+    <t>3d 12h</t>
+  </si>
+  <si>
+    <t>13d</t>
+  </si>
+  <si>
+    <t>Damage when destroyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>8d</t>
+  </si>
+  <si>
+    <t>13d 12h</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>After 1.5s</t>
+  </si>
+  <si>
+    <t>After 5.25s</t>
   </si>
 </sst>
 </file>
@@ -137,19 +272,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
@@ -157,16 +279,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFACD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -174,18 +327,152 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCECECE"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCECECE"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCECECE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCECECE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCECECE"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCECECE"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCECECE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCECECE"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCECECE"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCECECE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCECECE"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCECECE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCECECE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCECECE"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCECECE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -205,9 +492,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,7 +532,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -351,7 +638,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -493,7 +780,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -502,587 +789,589 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDC0AC2-6795-D34F-B3EF-6458DFDE8454}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="16" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="2" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>7</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>5.6</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>300</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>250</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>360</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>1000</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>5</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>13</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>10.4</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>420</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>4000</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>10</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>17</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>13.6</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>500</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>16000</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>34</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>23</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>18.399999999999999</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>600</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>50000</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>42</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>30</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>24</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>660</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>60000</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>60</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>40</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>32</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>730</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>100000</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>84</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>48</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>38.4</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>160000</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>103</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>56</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>44.8</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>880</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>250000</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>112</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>64</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>51.2</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>960</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>330000</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>120</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>74</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>59.2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>1060</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>500000</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>127</v>
       </c>
       <c r="H13" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>85</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>68</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
         <v>1160</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>600000</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>134</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>95</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>76</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="1">
         <v>1260</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>660000</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>146</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>100</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>80</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>1380</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>1000000</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>169</v>
       </c>
       <c r="H16" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>105</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>84</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
         <v>1500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>1200000</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>189</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>110</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>88</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1620</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>1300000</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="1">
         <v>198</v>
       </c>
       <c r="H18" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>115</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>92</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="1">
         <v>1740</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>1500000</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>207</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>125</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>100</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="1">
         <v>1870</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="1">
         <v>1800000</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="1">
         <v>240</v>
       </c>
       <c r="H20" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>135</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>108</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
         <v>2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>2000000</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="1">
         <v>268</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>150</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>120</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="1">
         <v>2150</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="1">
         <v>2600000</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="1">
         <v>293</v>
       </c>
       <c r="H22" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>160</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>128</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="1">
         <v>2250</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="1">
         <v>3000000</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="1">
         <v>360</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1093,4 +1382,4208 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7DF2D0-FB19-4D4C-A97F-2546A06192A3}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2">
+        <v>800</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.84</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10.24</v>
+      </c>
+      <c r="G3" s="2">
+        <v>102.4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2">
+        <v>207</v>
+      </c>
+      <c r="L3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F4" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>128</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="2">
+        <v>293</v>
+      </c>
+      <c r="L4" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2">
+        <v>120</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.12</v>
+      </c>
+      <c r="F5" s="2">
+        <v>15.36</v>
+      </c>
+      <c r="G5" s="2">
+        <v>153.6</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="2">
+        <v>415</v>
+      </c>
+      <c r="L5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2">
+        <v>140</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5.76</v>
+      </c>
+      <c r="F6" s="2">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="G6" s="2">
+        <v>179.2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3400000</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="2">
+        <v>464</v>
+      </c>
+      <c r="L6" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2">
+        <v>150</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>192</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I7" s="3">
+        <v>4200000</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="2">
+        <v>509</v>
+      </c>
+      <c r="L7" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2">
+        <v>160</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7.04</v>
+      </c>
+      <c r="F8" s="2">
+        <v>20.48</v>
+      </c>
+      <c r="G8" s="2">
+        <v>204.8</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="2">
+        <v>587</v>
+      </c>
+      <c r="L8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2">
+        <v>180</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E9" s="2">
+        <v>8.32</v>
+      </c>
+      <c r="F9" s="2">
+        <v>23.04</v>
+      </c>
+      <c r="G9" s="2">
+        <v>230.4</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="2">
+        <v>657</v>
+      </c>
+      <c r="L9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2">
+        <v>210</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="2">
+        <v>10.24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>26.88</v>
+      </c>
+      <c r="G10" s="2">
+        <v>268.8</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9500000</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="2">
+        <v>720</v>
+      </c>
+      <c r="L10" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2">
+        <v>230</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E11" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="F11" s="2">
+        <v>29.44</v>
+      </c>
+      <c r="G11" s="2">
+        <v>294.39999999999998</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I11" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="2">
+        <v>749</v>
+      </c>
+      <c r="L11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>120</v>
+      </c>
+      <c r="C12" s="2">
+        <v>260</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="2">
+        <v>15.36</v>
+      </c>
+      <c r="F12" s="2">
+        <v>33.28</v>
+      </c>
+      <c r="G12" s="2">
+        <v>332.8</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>11000000</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="2">
+        <v>777</v>
+      </c>
+      <c r="L12" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2">
+        <v>290</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E13" s="2">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="F13" s="2">
+        <v>37.119999999999997</v>
+      </c>
+      <c r="G13" s="2">
+        <v>371.2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I13" s="3">
+        <v>16000000</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="2">
+        <v>831</v>
+      </c>
+      <c r="L13" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>155</v>
+      </c>
+      <c r="C14" s="2">
+        <v>330</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="2">
+        <v>19.84</v>
+      </c>
+      <c r="F14" s="2">
+        <v>42.24</v>
+      </c>
+      <c r="G14" s="2">
+        <v>422.4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>26500000</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1080</v>
+      </c>
+      <c r="L14" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I1" r:id="rId1" location="Gold" tooltip="Resources" display="https://clashofclans.fandom.com/wiki/Resources - Gold" xr:uid="{D906D169-31D2-4504-9836-2475E7E6203A}"/>
+    <hyperlink ref="K1" r:id="rId2" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{FF5817D1-56F3-46F9-9CE0-48EE41817033}"/>
+    <hyperlink ref="L1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{A3428B6F-CEC9-4857-B1D7-6C9BC4C8D1FE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1D6D99-74DB-477D-86DB-4255257AECDB}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>380</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>420</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>460</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>34</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>500</v>
+      </c>
+      <c r="E6" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
+        <v>540</v>
+      </c>
+      <c r="E7" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="2">
+        <v>73</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>580</v>
+      </c>
+      <c r="E8" s="3">
+        <v>80000</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2">
+        <v>84</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2">
+        <v>630</v>
+      </c>
+      <c r="E9" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <v>103</v>
+      </c>
+      <c r="H9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2">
+        <v>690</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200000</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2">
+        <v>120</v>
+      </c>
+      <c r="H10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2">
+        <v>750</v>
+      </c>
+      <c r="E11" s="3">
+        <v>400000</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2">
+        <v>134</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>63</v>
+      </c>
+      <c r="C12" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>810</v>
+      </c>
+      <c r="E12" s="3">
+        <v>460000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2">
+        <v>146</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2">
+        <v>890</v>
+      </c>
+      <c r="E13" s="3">
+        <v>600000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="2">
+        <v>158</v>
+      </c>
+      <c r="H13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>74</v>
+      </c>
+      <c r="C14" s="2">
+        <v>37</v>
+      </c>
+      <c r="D14" s="2">
+        <v>970</v>
+      </c>
+      <c r="E14" s="3">
+        <v>700000</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2">
+        <v>169</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>78</v>
+      </c>
+      <c r="C15" s="2">
+        <v>39</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1050</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="2">
+        <v>189</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>82</v>
+      </c>
+      <c r="C16" s="2">
+        <v>41</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1130</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="2">
+        <v>198</v>
+      </c>
+      <c r="H16" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>85</v>
+      </c>
+      <c r="C17" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1230</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="2">
+        <v>207</v>
+      </c>
+      <c r="H17" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>90</v>
+      </c>
+      <c r="C18" s="2">
+        <v>45</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1310</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2">
+        <v>240</v>
+      </c>
+      <c r="H18" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>100</v>
+      </c>
+      <c r="C19" s="2">
+        <v>50</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1390</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="2">
+        <v>268</v>
+      </c>
+      <c r="H19" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>110</v>
+      </c>
+      <c r="C20" s="2">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1510</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2">
+        <v>293</v>
+      </c>
+      <c r="H20" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>120</v>
+      </c>
+      <c r="C21" s="2">
+        <v>60</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="2">
+        <v>328</v>
+      </c>
+      <c r="H21" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>135</v>
+      </c>
+      <c r="C22" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2">
+        <v>360</v>
+      </c>
+      <c r="H22" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6">
+        <v>145</v>
+      </c>
+      <c r="C23" s="6">
+        <v>72.5</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1800</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4000000</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="6">
+        <v>415</v>
+      </c>
+      <c r="H23" s="6">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{1E6268F9-3AE3-4040-9651-6F8AB8E2062D}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{B27CAF7B-3C68-46D1-8451-A81E4227A834}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5525F4-82AD-4200-B24E-77A0FACC75DF}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>400</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2">
+        <v>450</v>
+      </c>
+      <c r="E4" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>60</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>500</v>
+      </c>
+      <c r="E5" s="3">
+        <v>90000</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2">
+        <v>84</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2">
+        <v>550</v>
+      </c>
+      <c r="E6" s="3">
+        <v>180000</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>103</v>
+      </c>
+      <c r="H6" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2">
+        <v>600</v>
+      </c>
+      <c r="E7" s="3">
+        <v>300000</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2">
+        <v>146</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2">
+        <v>55</v>
+      </c>
+      <c r="D8" s="2">
+        <v>650</v>
+      </c>
+      <c r="E8" s="3">
+        <v>500000</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2">
+        <v>169</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>900000</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="2">
+        <v>207</v>
+      </c>
+      <c r="H9" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>100</v>
+      </c>
+      <c r="D10" s="2">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2">
+        <v>254</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>125</v>
+      </c>
+      <c r="D11" s="2">
+        <v>950</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="2">
+        <v>268</v>
+      </c>
+      <c r="H11" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2">
+        <v>150</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <v>293</v>
+      </c>
+      <c r="H12" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>175</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2">
+        <v>328</v>
+      </c>
+      <c r="H13" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2">
+        <v>190</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="2">
+        <v>360</v>
+      </c>
+      <c r="H14" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2">
+        <v>210</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="2">
+        <v>415</v>
+      </c>
+      <c r="H15" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2">
+        <v>240</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1950</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="2">
+        <v>464</v>
+      </c>
+      <c r="H16" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2150</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="2">
+        <v>509</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>60</v>
+      </c>
+      <c r="C18" s="2">
+        <v>300</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7000000</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="2">
+        <v>587</v>
+      </c>
+      <c r="H18" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>66</v>
+      </c>
+      <c r="C19" s="2">
+        <v>330</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2450</v>
+      </c>
+      <c r="E19" s="3">
+        <v>13000000</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="2">
+        <v>657</v>
+      </c>
+      <c r="H19" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2">
+        <v>360</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2550</v>
+      </c>
+      <c r="E20" s="3">
+        <v>21000000</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1039</v>
+      </c>
+      <c r="H20" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{56AD6977-D00D-4E3D-9E53-CDBA011011B2}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{09A68038-C988-4238-8BB1-16EBE7C79306}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A89C45-A6E4-4EAE-B1EF-C4889FB645C2}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>80</v>
+      </c>
+      <c r="C3" s="2">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2">
+        <v>800</v>
+      </c>
+      <c r="E3" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>60</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>110</v>
+      </c>
+      <c r="C4" s="2">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2">
+        <v>850</v>
+      </c>
+      <c r="E4" s="3">
+        <v>90000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2">
+        <v>84</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>140</v>
+      </c>
+      <c r="C5" s="2">
+        <v>140</v>
+      </c>
+      <c r="D5" s="2">
+        <v>900</v>
+      </c>
+      <c r="E5" s="3">
+        <v>210000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2">
+        <v>146</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>160</v>
+      </c>
+      <c r="C6" s="2">
+        <v>160</v>
+      </c>
+      <c r="D6" s="2">
+        <v>950</v>
+      </c>
+      <c r="E6" s="3">
+        <v>500000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2">
+        <v>207</v>
+      </c>
+      <c r="H6" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>190</v>
+      </c>
+      <c r="C7" s="2">
+        <v>190</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>800000</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2">
+        <v>254</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>230</v>
+      </c>
+      <c r="C8" s="2">
+        <v>230</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1050</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2">
+        <v>293</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>280</v>
+      </c>
+      <c r="C9" s="2">
+        <v>280</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1750000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2">
+        <v>415</v>
+      </c>
+      <c r="H9" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>320</v>
+      </c>
+      <c r="C10" s="2">
+        <v>320</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1210</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2">
+        <v>464</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>360</v>
+      </c>
+      <c r="C11" s="2">
+        <v>360</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3400000</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="2">
+        <v>509</v>
+      </c>
+      <c r="H11" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>400</v>
+      </c>
+      <c r="C12" s="2">
+        <v>400</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2">
+        <v>587</v>
+      </c>
+      <c r="H12" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>440</v>
+      </c>
+      <c r="C13" s="2">
+        <v>440</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5600000</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="2">
+        <v>623</v>
+      </c>
+      <c r="H13" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>500</v>
+      </c>
+      <c r="C14" s="2">
+        <v>500</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1650</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6500000</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2">
+        <v>657</v>
+      </c>
+      <c r="H14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>540</v>
+      </c>
+      <c r="C15" s="2">
+        <v>540</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1750</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="2">
+        <v>720</v>
+      </c>
+      <c r="H15" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>600</v>
+      </c>
+      <c r="C16" s="2">
+        <v>600</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1850</v>
+      </c>
+      <c r="E16" s="3">
+        <v>9000000</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="2">
+        <v>749</v>
+      </c>
+      <c r="H16" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>650</v>
+      </c>
+      <c r="C17" s="2">
+        <v>650</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1950</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15000000</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="2">
+        <v>777</v>
+      </c>
+      <c r="H17" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>700</v>
+      </c>
+      <c r="C18" s="2">
+        <v>700</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>26000000</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1069</v>
+      </c>
+      <c r="H18" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{9B7042E2-8DFF-4B44-BEB3-390C821D206C}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{46A81A48-E9BB-42F5-9F91-DAF2788C3E09}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE5F138-2B50-4E60-9222-4BFEC8037B68}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>620</v>
+      </c>
+      <c r="E3" s="3">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>60</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D4" s="2">
+        <v>650</v>
+      </c>
+      <c r="E4" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2">
+        <v>73</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>680</v>
+      </c>
+      <c r="E5" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>120</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
+        <v>730</v>
+      </c>
+      <c r="E6" s="3">
+        <v>400000</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
+        <v>169</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
+        <v>31.2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>840</v>
+      </c>
+      <c r="E7" s="3">
+        <v>550000</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="2">
+        <v>189</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2">
+        <v>41.6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>960</v>
+      </c>
+      <c r="E8" s="3">
+        <v>660000</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="2">
+        <v>207</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="2">
+        <v>254</v>
+      </c>
+      <c r="H9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2">
+        <v>58.5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1440</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="2">
+        <v>268</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2">
+        <v>293</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2">
+        <v>328</v>
+      </c>
+      <c r="H12" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2">
+        <v>91</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2120</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="2">
+        <v>360</v>
+      </c>
+      <c r="H13" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>78</v>
+      </c>
+      <c r="C14" s="2">
+        <v>101.4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2240</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="2">
+        <v>388</v>
+      </c>
+      <c r="H14" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>84</v>
+      </c>
+      <c r="C15" s="2">
+        <v>109.2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="2">
+        <v>415</v>
+      </c>
+      <c r="H15" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>90</v>
+      </c>
+      <c r="C16" s="2">
+        <v>117</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4500000</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="2">
+        <v>509</v>
+      </c>
+      <c r="H16" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>95</v>
+      </c>
+      <c r="C17" s="2">
+        <v>123.5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5500000</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="2">
+        <v>587</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>102</v>
+      </c>
+      <c r="C18" s="2">
+        <v>132.6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3150</v>
+      </c>
+      <c r="E18" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2">
+        <v>623</v>
+      </c>
+      <c r="H18" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6">
+        <v>110</v>
+      </c>
+      <c r="C19" s="6">
+        <v>143</v>
+      </c>
+      <c r="D19" s="7">
+        <v>3300</v>
+      </c>
+      <c r="E19" s="7">
+        <v>14000000</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="6">
+        <v>689</v>
+      </c>
+      <c r="H19" s="6">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{66DF7AF9-D422-4CE8-B6A8-F6B9103B76EE}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{C1976C3E-F17D-4AE2-9D6A-6A2EB97D1AC9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66F7A90-D2E0-4033-BB9F-BD33A993C1C5}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2">
+        <v>800</v>
+      </c>
+      <c r="D4" s="3">
+        <v>300000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2">
+        <v>146</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2">
+        <v>850</v>
+      </c>
+      <c r="D5" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2">
+        <v>169</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="2">
+        <v>900</v>
+      </c>
+      <c r="D6" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2">
+        <v>207</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2">
+        <v>950</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2">
+        <v>293</v>
+      </c>
+      <c r="G7" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2">
+        <v>415</v>
+      </c>
+      <c r="G8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1050</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3400000</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="2">
+        <v>509</v>
+      </c>
+      <c r="G9" s="2">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" location="Gold" tooltip="Resources" display="https://clashofclans.fandom.com/wiki/Resources - Gold" xr:uid="{F03C51CB-594E-494C-8C30-587C91DD5340}"/>
+    <hyperlink ref="F1" r:id="rId2" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{06AB7AA3-364D-4E9A-8E20-2A1DF839E5BF}"/>
+    <hyperlink ref="G1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{3D60F556-C879-43F4-B596-1CFD39921C3A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C31C319-67B8-45CC-B1FD-E9FD3CEF693A}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D3" s="4">
+        <v>600</v>
+      </c>
+      <c r="E3" s="18">
+        <v>250000</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="4">
+        <v>84</v>
+      </c>
+      <c r="H3" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4">
+        <v>630</v>
+      </c>
+      <c r="E4" s="18">
+        <v>350000</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4">
+        <v>103</v>
+      </c>
+      <c r="H4" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
+        <v>48</v>
+      </c>
+      <c r="C5" s="4">
+        <v>28.8</v>
+      </c>
+      <c r="D5" s="4">
+        <v>660</v>
+      </c>
+      <c r="E5" s="18">
+        <v>500000</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4">
+        <v>120</v>
+      </c>
+      <c r="H5" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>55</v>
+      </c>
+      <c r="C6" s="4">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <v>690</v>
+      </c>
+      <c r="E6" s="18">
+        <v>600000</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4">
+        <v>146</v>
+      </c>
+      <c r="H6" s="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
+        <v>64</v>
+      </c>
+      <c r="C7" s="4">
+        <v>38.4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>730</v>
+      </c>
+      <c r="E7" s="18">
+        <v>800000</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4">
+        <v>207</v>
+      </c>
+      <c r="H7" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>75</v>
+      </c>
+      <c r="C8" s="4">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4">
+        <v>770</v>
+      </c>
+      <c r="E8" s="18">
+        <v>1200000</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="4">
+        <v>293</v>
+      </c>
+      <c r="H8" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>87</v>
+      </c>
+      <c r="C9" s="4">
+        <v>52.2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>810</v>
+      </c>
+      <c r="E9" s="18">
+        <v>1400000</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="4">
+        <v>328</v>
+      </c>
+      <c r="H9" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>99</v>
+      </c>
+      <c r="C10" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="D10" s="4">
+        <v>850</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1600000</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4">
+        <v>360</v>
+      </c>
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4">
+        <v>110</v>
+      </c>
+      <c r="C11" s="4">
+        <v>66</v>
+      </c>
+      <c r="D11" s="4">
+        <v>900</v>
+      </c>
+      <c r="E11" s="18">
+        <v>2100000</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="4">
+        <v>388</v>
+      </c>
+      <c r="H11" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <v>120</v>
+      </c>
+      <c r="C12" s="4">
+        <v>72</v>
+      </c>
+      <c r="D12" s="4">
+        <v>980</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3000000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="4">
+        <v>415</v>
+      </c>
+      <c r="H12" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>130</v>
+      </c>
+      <c r="C13" s="4">
+        <v>78</v>
+      </c>
+      <c r="D13" s="18">
+        <v>1100</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3100000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="4">
+        <v>464</v>
+      </c>
+      <c r="H13" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>140</v>
+      </c>
+      <c r="C14" s="4">
+        <v>84</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3700000</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="4">
+        <v>509</v>
+      </c>
+      <c r="H14" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>150</v>
+      </c>
+      <c r="C15" s="4">
+        <v>90</v>
+      </c>
+      <c r="D15" s="18">
+        <v>1350</v>
+      </c>
+      <c r="E15" s="18">
+        <v>5100000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="4">
+        <v>549</v>
+      </c>
+      <c r="H15" s="19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4">
+        <v>160</v>
+      </c>
+      <c r="C16" s="4">
+        <v>96</v>
+      </c>
+      <c r="D16" s="18">
+        <v>1450</v>
+      </c>
+      <c r="E16" s="18">
+        <v>6500000</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="4">
+        <v>587</v>
+      </c>
+      <c r="H16" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4">
+        <v>170</v>
+      </c>
+      <c r="C17" s="4">
+        <v>102</v>
+      </c>
+      <c r="D17" s="18">
+        <v>1550</v>
+      </c>
+      <c r="E17" s="18">
+        <v>8200000</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="4">
+        <v>657</v>
+      </c>
+      <c r="H17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>180</v>
+      </c>
+      <c r="C18" s="4">
+        <v>108</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1650</v>
+      </c>
+      <c r="E18" s="18">
+        <v>15000000</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="4">
+        <v>777</v>
+      </c>
+      <c r="H18" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4">
+        <v>190</v>
+      </c>
+      <c r="C19" s="4">
+        <v>114</v>
+      </c>
+      <c r="D19" s="18">
+        <v>1750</v>
+      </c>
+      <c r="E19" s="18">
+        <v>25000000</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1059</v>
+      </c>
+      <c r="H19" s="4">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E1" r:id="rId1" location="Gold" tooltip="Resources" display="https://clashofclans.fandom.com/wiki/Resources - Gold" xr:uid="{DDC50836-46BA-4F78-BBD3-1651A721EB0E}"/>
+    <hyperlink ref="G1" r:id="rId2" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{41412CEB-C73F-4385-9BFD-468CB44FE6FE}"/>
+    <hyperlink ref="H1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{8EB03270-59F1-4C11-BB5A-CECD9A230668}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DA5049-FAB0-47AB-B3EF-88E99E0293C2}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="D3" s="2">
+        <v>150</v>
+      </c>
+      <c r="E3" s="2">
+        <v>650</v>
+      </c>
+      <c r="F3" s="3">
+        <v>700000</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2">
+        <v>207</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
+        <v>30.8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>180</v>
+      </c>
+      <c r="E4" s="2">
+        <v>700</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2">
+        <v>254</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D5" s="2">
+        <v>220</v>
+      </c>
+      <c r="E5" s="2">
+        <v>750</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2">
+        <v>293</v>
+      </c>
+      <c r="I5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2">
+        <v>260</v>
+      </c>
+      <c r="E6" s="2">
+        <v>850</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2">
+        <v>360</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>52.8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>300</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1050</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="2">
+        <v>388</v>
+      </c>
+      <c r="I7" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2">
+        <v>61.6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>350</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2">
+        <v>415</v>
+      </c>
+      <c r="I8" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>64</v>
+      </c>
+      <c r="C9" s="2">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="D9" s="2">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2">
+        <v>509</v>
+      </c>
+      <c r="I9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>72</v>
+      </c>
+      <c r="C10" s="2">
+        <v>79.2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>450</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2">
+        <v>549</v>
+      </c>
+      <c r="I10" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2">
+        <v>92.4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>500</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="2">
+        <v>587</v>
+      </c>
+      <c r="I11" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>94</v>
+      </c>
+      <c r="C12" s="2">
+        <v>103.4</v>
+      </c>
+      <c r="D12" s="2">
+        <v>550</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7000000</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="2">
+        <v>623</v>
+      </c>
+      <c r="I12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>104</v>
+      </c>
+      <c r="C13" s="2">
+        <v>114.4</v>
+      </c>
+      <c r="D13" s="2">
+        <v>600</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F13" s="3">
+        <v>8500000</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="2">
+        <v>657</v>
+      </c>
+      <c r="I13" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>114</v>
+      </c>
+      <c r="C14" s="2">
+        <v>125.4</v>
+      </c>
+      <c r="D14" s="2">
+        <v>650</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>14500000</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2">
+        <v>777</v>
+      </c>
+      <c r="I14" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6">
+        <v>122</v>
+      </c>
+      <c r="C15" s="6">
+        <v>134.19999999999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>700</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3050</v>
+      </c>
+      <c r="F15" s="7">
+        <v>25000000</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1059</v>
+      </c>
+      <c r="I15" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{9D78CDE0-89C2-4A32-8378-784E70112E40}"/>
+    <hyperlink ref="I1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{E5CECCF3-9332-490D-B5CA-9189F65D2DBB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C75220-4EEA-4123-B913-08CF8A8B8A6A}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>60</v>
+      </c>
+      <c r="C3" s="2">
+        <v>7.68</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2">
+        <v>207</v>
+      </c>
+      <c r="H3" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2">
+        <v>293</v>
+      </c>
+      <c r="H4" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10.24</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2">
+        <v>415</v>
+      </c>
+      <c r="H5" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10.88</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2">
+        <v>464</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2">
+        <v>12.16</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3900000</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="2">
+        <v>509</v>
+      </c>
+      <c r="H7" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>110</v>
+      </c>
+      <c r="C8" s="2">
+        <v>14.08</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2">
+        <v>549</v>
+      </c>
+      <c r="H8" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2">
+        <v>16.64</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="2">
+        <v>587</v>
+      </c>
+      <c r="H9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>155</v>
+      </c>
+      <c r="C10" s="2">
+        <v>19.84</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7000000</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2">
+        <v>623</v>
+      </c>
+      <c r="H10" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>185</v>
+      </c>
+      <c r="C11" s="2">
+        <v>23.68</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E11" s="3">
+        <v>9000000</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="2">
+        <v>657</v>
+      </c>
+      <c r="H11" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>205</v>
+      </c>
+      <c r="C12" s="2">
+        <v>26.24</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9500000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="2">
+        <v>689</v>
+      </c>
+      <c r="H12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>225</v>
+      </c>
+      <c r="C13" s="2">
+        <v>28.8</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="2">
+        <v>720</v>
+      </c>
+      <c r="H13" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6">
+        <v>235</v>
+      </c>
+      <c r="C14" s="6">
+        <v>30.08</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="7">
+        <v>16000000</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="6">
+        <v>831</v>
+      </c>
+      <c r="H14" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>245</v>
+      </c>
+      <c r="C15" s="2">
+        <v>31.36</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>26000000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1080</v>
+      </c>
+      <c r="H15" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{07C813A8-6281-49BD-BAAB-50B7EA26671E}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{26FF0F49-DDE5-4D28-ADA5-16D1D0DB360F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/info/defences/defencesDatabase.xlsx
+++ b/info/defences/defencesDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\arxstudios\clashex\info\defences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AA3C6D-8EC6-454A-B32B-E2E65A561D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B856CF-7F9E-4E1F-91D2-54BE8F94C4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="19296" tabRatio="779" firstSheet="1" activeTab="9" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
+    <workbookView xWindow="16365" yWindow="0" windowWidth="35340" windowHeight="13575" tabRatio="779" firstSheet="1" activeTab="12" xr2:uid="{2CC304E0-977A-F44C-9ED5-57AAFC62DE41}"/>
   </bookViews>
   <sheets>
     <sheet name="cannon" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="bomb tower" sheetId="8" r:id="rId8"/>
     <sheet name="xbow" sheetId="9" r:id="rId9"/>
     <sheet name="Inferno_Tower" sheetId="10" r:id="rId10"/>
+    <sheet name="eagle_artilery" sheetId="11" r:id="rId11"/>
+    <sheet name="scattershot" sheetId="12" r:id="rId12"/>
+    <sheet name="builders_hut" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="98">
   <si>
     <t>Level</t>
   </si>
@@ -258,6 +261,87 @@
   <si>
     <t>After 5.25s</t>
   </si>
+  <si>
+    <t>Shockwave Damage</t>
+  </si>
+  <si>
+    <t>7d 12h</t>
+  </si>
+  <si>
+    <t>9d</t>
+  </si>
+  <si>
+    <t>9d 12h</t>
+  </si>
+  <si>
+    <t>Damage per Shot*</t>
+  </si>
+  <si>
+    <t>Splash Damage**</t>
+  </si>
+  <si>
+    <t>300-400</t>
+  </si>
+  <si>
+    <t>100-300</t>
+  </si>
+  <si>
+    <t>360-480</t>
+  </si>
+  <si>
+    <t>120-360</t>
+  </si>
+  <si>
+    <t>380-544</t>
+  </si>
+  <si>
+    <t>130-380</t>
+  </si>
+  <si>
+    <t>400-560</t>
+  </si>
+  <si>
+    <t>140-400</t>
+  </si>
+  <si>
+    <t>420-576</t>
+  </si>
+  <si>
+    <t>150-420</t>
+  </si>
+  <si>
+    <t>8d 12h</t>
+  </si>
+  <si>
+    <t>440-592</t>
+  </si>
+  <si>
+    <t>155-440</t>
+  </si>
+  <si>
+    <t>450-608</t>
+  </si>
+  <si>
+    <t>160-450</t>
+  </si>
+  <si>
+    <t>15d</t>
+  </si>
+  <si>
+    <t>Repair per Second</t>
+  </si>
+  <si>
+    <t>Repair per Hit</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Varies**</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
 </sst>
 </file>
 
@@ -404,7 +488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -448,7 +532,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -473,6 +556,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -489,6 +584,3534 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2049" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D5C30D2-5A9D-131D-88CF-7899EE6F3837}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2050" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AA0E5C2-5060-923D-7302-86A80338E238}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="400050" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2051" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1955742A-E48F-A109-B04E-D470F03E9E13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="857250" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2052" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7970BAAF-552E-F94D-EEAB-9B07BC7ED6FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1390650" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2053" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1835650F-804A-83B3-3B05-AE0D1CD31330}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2047875" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2054" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B32D62-2BEF-12DD-7687-85D78C72ACD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2752725" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2055" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2A15C0-C646-3844-6EDB-B0E9EC8955C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3467100" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2056" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7EFF6D7-516C-4208-5A95-0D9808E11426}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3771900" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3073" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEC3D6EE-8FB4-0DD0-D9DA-A0102272FF25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3074" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B8D4D4C-59E3-072D-0DB8-47C7DD67F16F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="390525" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3075" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B696BE59-AD44-E142-CB4D-518388D15182}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3076" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{795B554A-A662-E4F7-146B-6D7A0B7BF1F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1343025" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3077" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03BB5564-7AB0-EE07-E6A3-496DCBD149F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1971675" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3078" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB3F2BD-AE4A-09E2-8BF8-630FB441FFF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2762250" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3079" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{213DAF08-2754-6C65-CBEA-5C6531DD57E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3457575" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3080" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8082928E-2088-E893-9931-9F38CB1F31ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3867150" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4097" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{632FAEBB-1A69-A1DE-88DE-B049A1DEC24B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4098" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{796F26B2-7AFB-E75B-3BC1-F7B4081ACFEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="390525" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4099" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB02918-9943-FB55-ACC3-820BBA2EF061}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4100" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDFF671-3721-6FDD-42EA-4876A9088BD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1343025" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4101" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A88DF35C-ED56-B42D-2982-CA39A7BE16FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1971675" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4102" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ACDE5CA-CEBE-4354-6B7B-BD200C517119}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2762250" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4103" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44086EA2-5205-265A-3CEE-8EC4AEB5FFC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3457575" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4104" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB41BD3-2A53-BF53-3F31-32976051876D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3867150" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5121" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4450B3-4752-833D-243E-68C962382D52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5122" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B307B848-F550-AAA3-9126-ACF420C1885C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="390525" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5123" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A320DA-01D7-EE7B-9E62-91DF827D1A21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5124" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4CAD8F4-F8D2-3E05-81AE-CA1D20D3ED9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1343025" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5125" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B5456D1-520F-F0BC-D8BC-EA82B21A862E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1971675" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5126" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B91E5F4E-647B-FDFA-1984-7FEDA8913A7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2762250" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5127" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57FFF3C2-DCB0-2253-FCA2-8C88CE8C6C04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3457575" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5128" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C656C2D6-F1A0-3630-9BA3-DE6ED8C0076C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3752850" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6145" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{658CD397-42BC-B0F2-0E54-79E285A43D5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6146" name="AutoShape 2" descr="Push Strength">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B84E6866-551F-FFF0-784D-FDEA2194FE42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="685800" y="390525"/>
+          <a:ext cx="247650" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6147" name="AutoShape 3" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21500E93-530B-5F5A-3DDD-E317C417EBE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6148" name="AutoShape 4" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5C01CD-B722-C622-119B-4CA27688D048}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2057400" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6149" name="AutoShape 5" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E6636D9-EB6C-F907-6CDB-38FE62C0DB49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2743200" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6150" name="AutoShape 6" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901174C3-1E38-8A60-3207-F962AF1B8D5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3429000" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6151" name="AutoShape 7" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{507F983C-86D7-E747-9D6E-2B7DA304E94C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4114800" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7169" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8336500A-7498-EC15-AA8D-0F2D988E1CE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7170" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F19EE21-6B13-5B18-E184-5150941DD07D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="447675" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7171" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ECD2199-DE85-B12F-C4D3-BCAD2972392A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1895475" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7172" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42CFF785-FBF5-BA68-D429-217042DD11AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3133725" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7173" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7717F60C-D6FE-D1AB-0013-A01810CF4F06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3810000" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7174" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCE2A55-159A-A44F-B6B9-27DE9BFCED63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4600575" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7175" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D376C5-FD97-44E9-B83B-882EAC1BC473}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5391150" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7176" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A4C7EF1-1B98-278D-D744-F819F008B519}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6619875" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8193" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0AF8F49-01C7-AEB5-886C-82ADF4D1635B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="552450"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8194" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE4EB2F4-60E0-3325-F555-F57E3AE30A9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="685800" y="552450"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8195" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE9A1DFF-02DD-D71F-7A42-372B2700A6C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="552450"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8196" name="AutoShape 4" descr="Death Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{385301B4-16FF-D4E6-0501-DEB01DA7AB14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2057400" y="552450"/>
+          <a:ext cx="161925" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8197" name="AutoShape 5" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA5D985-4E6E-6B04-85F4-D975F8DC3582}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2743200" y="552450"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8198" name="AutoShape 6" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A2FA20-25F7-BFE4-E1EC-2135533B9485}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3429000" y="552450"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8199" name="AutoShape 7" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50C7C85E-E726-234F-DB00-39D8DC3B2608}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4114800" y="552450"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8200" name="AutoShape 8" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{507659FF-3A2C-B325-3CFF-59F8ABF97C31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4800600" y="552450"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8201" name="AutoShape 9" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{236B8A10-4183-6A60-FC91-F0DF314131B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5486400" y="552450"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9217" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EC00C98-B0A6-F5A5-A58E-1ACF981ED456}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="390525"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9218" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7193B6-BC2C-B08D-5B7B-058738E45A63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="685800" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9219" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5FBB66F-C537-A4F8-22C8-D97203F80C49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="390525"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9220" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93D894A9-8792-5B67-FDDF-05DE5AB43009}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2057400" y="390525"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9221" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A09A555C-C384-B064-E19C-52A9ED746347}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2743200" y="390525"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9222" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47ADA745-E709-DAA1-94A9-DB80FF9CE3C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3429000" y="390525"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9223" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97831016-A718-5342-CEB4-2AE230DDEFA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4114800" y="390525"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9224" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53696F0C-E721-D732-CA47-9E1FA18E1468}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4800600" y="390525"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10241" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD6D4E4-E5A2-9E80-97EA-316501D60296}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="609600"/>
+          <a:ext cx="161925" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10242" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DDC1BC8-9433-8DF7-6801-87D660BC0B24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="447675" y="609600"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10243" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22A1E75E-9E62-1DB5-BDCF-A52BA4499F44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1857375" y="609600"/>
+          <a:ext cx="266700" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10244" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{118FE547-98CA-2F75-FC93-4101ECADC7EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3286125" y="609600"/>
+          <a:ext cx="190500" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10245" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5D0397D-4C00-FB3B-9443-8280674AB8D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3962400" y="609600"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10246" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41BFA083-C10E-1DE4-B581-357382DCB29D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4752975" y="609600"/>
+          <a:ext cx="171450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10247" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C90D0054-9353-6728-8B28-25E205768886}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5314950" y="609600"/>
+          <a:ext cx="209550" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10248" name="AutoShape 8" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E938D605-1A97-24B6-ED85-FCAF1CF1682A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5981700" y="609600"/>
+          <a:ext cx="247650" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1385,7 +5008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7DF2D0-FB19-4D4C-A97F-2546A06192A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7DF2D0-FB19-4D4C-A97F-2546A06192A3}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1406,16 +5029,16 @@
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="21" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="11" t="s">
         <v>1</v>
       </c>
@@ -1434,22 +5057,22 @@
     </row>
     <row r="2" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>70</v>
       </c>
       <c r="H2" s="12"/>
@@ -1921,12 +5544,881 @@
     <hyperlink ref="L1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{A3428B6F-CEC9-4857-B1D7-6C9BC4C8D1FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4FCA02-808B-4CE7-B3AD-DCB63BDF9EC4}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>225</v>
+      </c>
+      <c r="C3" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="2">
+        <v>587</v>
+      </c>
+      <c r="I3" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>250</v>
+      </c>
+      <c r="C4" s="2">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="2">
+        <v>657</v>
+      </c>
+      <c r="I4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>275</v>
+      </c>
+      <c r="C5" s="2">
+        <v>82.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F5" s="3">
+        <v>9000000</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="2">
+        <v>777</v>
+      </c>
+      <c r="I5" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>350</v>
+      </c>
+      <c r="C6" s="2">
+        <v>105</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F6" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="2">
+        <v>804</v>
+      </c>
+      <c r="I6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>425</v>
+      </c>
+      <c r="C7" s="2">
+        <v>127.5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F7" s="3">
+        <v>12000000</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="2">
+        <v>831</v>
+      </c>
+      <c r="I7" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>475</v>
+      </c>
+      <c r="C8" s="2">
+        <v>142.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>13000000</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="2">
+        <v>881</v>
+      </c>
+      <c r="I8" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>525</v>
+      </c>
+      <c r="C9" s="2">
+        <v>157.5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>14000000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="2">
+        <v>905</v>
+      </c>
+      <c r="I9" s="2">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F1" r:id="rId1" location="Gold" tooltip="Resources" display="https://clashofclans.fandom.com/wiki/Resources - Gold" xr:uid="{B7BB9DC7-C512-4B94-BBD2-0CFEFEE7615B}"/>
+    <hyperlink ref="H1" r:id="rId2" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{F93174A6-0696-4888-8FFB-068B66DD0F33}"/>
+    <hyperlink ref="I1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{6C43EFE0-2650-46FB-B947-0AA7B19EE3F2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF96E9F-A3FD-45B2-9FA7-D1D451470D9F}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="2">
+        <v>657</v>
+      </c>
+      <c r="I3" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>150</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F4" s="3">
+        <v>9000000</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2">
+        <v>777</v>
+      </c>
+      <c r="I4" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>170</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F5" s="3">
+        <v>11000000</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="2">
+        <v>804</v>
+      </c>
+      <c r="I5" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>175</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F6" s="3">
+        <v>11500000</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="2">
+        <v>831</v>
+      </c>
+      <c r="I6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>180</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5410</v>
+      </c>
+      <c r="F7" s="3">
+        <v>12000000</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="2">
+        <v>856</v>
+      </c>
+      <c r="I7" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>185</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>16500000</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="2">
+        <v>881</v>
+      </c>
+      <c r="I8" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>190</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>26500000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1138</v>
+      </c>
+      <c r="I9" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{D2D44159-80E9-43D3-9A35-26EF8282839D}"/>
+    <hyperlink ref="I1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{8338D27D-C5B5-4F6A-9D06-DB63F7CCABDA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B858BC41-7FD2-417A-8E9C-A0F8848E045A}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="2">
+        <v>250</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="2">
+        <v>415</v>
+      </c>
+      <c r="J4" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>100</v>
+      </c>
+      <c r="C5" s="2">
+        <v>40</v>
+      </c>
+      <c r="D5" s="2">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="2">
+        <v>509</v>
+      </c>
+      <c r="J5" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>120</v>
+      </c>
+      <c r="C6" s="2">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G6" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="2">
+        <v>587</v>
+      </c>
+      <c r="J6" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>135</v>
+      </c>
+      <c r="C7" s="2">
+        <v>54</v>
+      </c>
+      <c r="D7" s="2">
+        <v>80</v>
+      </c>
+      <c r="E7" s="2">
+        <v>60</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7000000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="2">
+        <v>657</v>
+      </c>
+      <c r="J7" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>150</v>
+      </c>
+      <c r="C8" s="2">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2">
+        <v>85</v>
+      </c>
+      <c r="E8" s="2">
+        <v>63.75</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G8" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="2">
+        <v>689</v>
+      </c>
+      <c r="J8" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>165</v>
+      </c>
+      <c r="C9" s="2">
+        <v>66</v>
+      </c>
+      <c r="D9" s="2">
+        <v>90</v>
+      </c>
+      <c r="E9" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>15500000</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2">
+        <v>777</v>
+      </c>
+      <c r="J9" s="2">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I1" r:id="rId1" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{610CA81C-6FC1-45A3-92DC-3613DC8C102F}"/>
+    <hyperlink ref="J1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{3ECABA3C-DDDB-413E-93A6-EBE8A8F2B12D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1D6D99-74DB-477D-86DB-4255257AECDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1D6D99-74DB-477D-86DB-4255257AECDB}">
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2528,12 +7020,12 @@
     <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{B27CAF7B-3C68-46D1-8451-A81E4227A834}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5525F4-82AD-4200-B24E-77A0FACC75DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5525F4-82AD-4200-B24E-77A0FACC75DF}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3057,12 +7549,12 @@
     <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{09A68038-C988-4238-8BB1-16EBE7C79306}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A89C45-A6E4-4EAE-B1EF-C4889FB645C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A89C45-A6E4-4EAE-B1EF-C4889FB645C2}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3534,12 +8026,12 @@
     <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{46A81A48-E9BB-42F5-9F91-DAF2788C3E09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE5F138-2B50-4E60-9222-4BFEC8037B68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE5F138-2B50-4E60-9222-4BFEC8037B68}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4037,12 +8529,12 @@
     <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{C1976C3E-F17D-4AE2-9D6A-6A2EB97D1AC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66F7A90-D2E0-4033-BB9F-BD33A993C1C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66F7A90-D2E0-4033-BB9F-BD33A993C1C5}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4246,23 +8738,22 @@
     <hyperlink ref="G1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{3D60F556-C879-43F4-B596-1CFD39921C3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C31C319-67B8-45CC-B1FD-E9FD3CEF693A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C31C319-67B8-45CC-B1FD-E9FD3CEF693A}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4292,14 +8783,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
@@ -4314,7 +8805,7 @@
       <c r="D3" s="4">
         <v>600</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>250000</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -4340,7 +8831,7 @@
       <c r="D4" s="4">
         <v>630</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>350000</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -4366,7 +8857,7 @@
       <c r="D5" s="4">
         <v>660</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>500000</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -4392,7 +8883,7 @@
       <c r="D6" s="4">
         <v>690</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>600000</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -4401,7 +8892,7 @@
       <c r="G6" s="4">
         <v>146</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>8</v>
       </c>
     </row>
@@ -4418,7 +8909,7 @@
       <c r="D7" s="4">
         <v>730</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>800000</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -4444,7 +8935,7 @@
       <c r="D8" s="4">
         <v>770</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>1200000</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -4470,7 +8961,7 @@
       <c r="D9" s="4">
         <v>810</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>1400000</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -4479,7 +8970,7 @@
       <c r="G9" s="4">
         <v>328</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <v>9</v>
       </c>
     </row>
@@ -4496,7 +8987,7 @@
       <c r="D10" s="4">
         <v>850</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>1600000</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -4522,7 +9013,7 @@
       <c r="D11" s="4">
         <v>900</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>2100000</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -4548,7 +9039,7 @@
       <c r="D12" s="4">
         <v>980</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>3000000</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -4571,10 +9062,10 @@
       <c r="C13" s="4">
         <v>78</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>1100</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>3100000</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -4597,10 +9088,10 @@
       <c r="C14" s="4">
         <v>84</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>1200</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>3700000</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -4623,10 +9114,10 @@
       <c r="C15" s="4">
         <v>90</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <v>1350</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>5100000</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -4635,7 +9126,7 @@
       <c r="G15" s="4">
         <v>549</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>14</v>
       </c>
     </row>
@@ -4649,10 +9140,10 @@
       <c r="C16" s="4">
         <v>96</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>1450</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>6500000</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -4675,10 +9166,10 @@
       <c r="C17" s="4">
         <v>102</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>1550</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>8200000</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -4701,10 +9192,10 @@
       <c r="C18" s="4">
         <v>108</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>1650</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>15000000</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -4727,16 +9218,16 @@
       <c r="C19" s="4">
         <v>114</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>1750</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>25000000</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <v>1059</v>
       </c>
       <c r="H19" s="4">
@@ -4750,12 +9241,12 @@
     <hyperlink ref="H1" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{8EB03270-59F1-4C11-BB5A-CECD9A230668}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DA5049-FAB0-47AB-B3EF-88E99E0293C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DA5049-FAB0-47AB-B3EF-88E99E0293C2}">
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5195,12 +9686,12 @@
     <hyperlink ref="I1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{E5CECCF3-9332-490D-B5CA-9189F65D2DBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C75220-4EEA-4123-B913-08CF8A8B8A6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C75220-4EEA-4123-B913-08CF8A8B8A6A}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5584,6 +10075,6 @@
     <hyperlink ref="H1" r:id="rId2" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{26FF0F49-DDE5-4D28-ADA5-16D1D0DB360F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>